--- a/12603564.xlsx
+++ b/12603564.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c6fb59ddac9459a3/Desktop/excel776/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="117" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22072AA5-D29F-42A2-AD45-AA722825B115}"/>
+  <xr:revisionPtr revIDLastSave="128" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0677A29E-A02B-4CF8-8E03-E458978DBF31}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1493,25 +1493,47 @@
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B17" s="14">
+        <v>400</v>
+      </c>
+      <c r="C17" s="14">
+        <v>20</v>
+      </c>
+      <c r="D17" s="14">
+        <v>240</v>
+      </c>
+      <c r="E17" s="14">
+        <v>180</v>
+      </c>
+      <c r="F17" s="14">
+        <v>250</v>
+      </c>
+      <c r="G17" s="14">
+        <v>5</v>
+      </c>
+      <c r="H17" s="14">
+        <v>30</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
+        <v>320</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">

--- a/12603564.xlsx
+++ b/12603564.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c6fb59ddac9459a3/Desktop/excel776/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="128" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0677A29E-A02B-4CF8-8E03-E458978DBF31}"/>
+  <xr:revisionPtr revIDLastSave="139" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36CB1967-9D02-4F71-A9C9-12B0CEB4B376}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1537,25 +1537,47 @@
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46235</v>
+      </c>
+      <c r="B18" s="14">
+        <v>360</v>
+      </c>
+      <c r="C18" s="14">
+        <v>10</v>
+      </c>
+      <c r="D18" s="14">
+        <v>200</v>
+      </c>
+      <c r="E18" s="14">
+        <v>120</v>
+      </c>
+      <c r="F18" s="14">
+        <v>3</v>
+      </c>
+      <c r="G18" s="14">
+        <v>3</v>
+      </c>
+      <c r="H18" s="14">
+        <v>10</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>703</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
+        <v>737</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">

--- a/12603564.xlsx
+++ b/12603564.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c6fb59ddac9459a3/Desktop/excel776/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="139" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36CB1967-9D02-4F71-A9C9-12B0CEB4B376}"/>
+  <xr:revisionPtr revIDLastSave="153" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2A18874-BB49-4408-BEFA-2558E86B37AA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -233,6 +233,9 @@
   </si>
   <si>
     <t>high</t>
+  </si>
+  <si>
+    <t>avarage</t>
   </si>
 </sst>
 </file>
@@ -1538,7 +1541,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="13">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="B18" s="14">
         <v>360</v>
@@ -1553,7 +1556,7 @@
         <v>120</v>
       </c>
       <c r="F18" s="14">
-        <v>3</v>
+        <v>150</v>
       </c>
       <c r="G18" s="14">
         <v>3</v>
@@ -1563,11 +1566,11 @@
       </c>
       <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v>703</v>
+        <v>850</v>
       </c>
       <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v>737</v>
+        <v>590</v>
       </c>
       <c r="K18" s="16" t="s">
         <v>59</v>
@@ -1581,25 +1584,47 @@
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B19" s="14">
+        <v>360</v>
+      </c>
+      <c r="C19" s="14">
+        <v>10</v>
+      </c>
+      <c r="D19" s="14">
+        <v>200</v>
+      </c>
+      <c r="E19" s="14">
+        <v>100</v>
+      </c>
+      <c r="F19" s="14">
+        <v>400</v>
+      </c>
+      <c r="G19" s="14">
+        <v>8</v>
+      </c>
+      <c r="H19" s="14">
+        <v>10</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
+        <v>360</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="N19" s="17"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">

--- a/12603564.xlsx
+++ b/12603564.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c6fb59ddac9459a3/Desktop/excel776/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="153" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2A18874-BB49-4408-BEFA-2558E86B37AA}"/>
+  <xr:revisionPtr revIDLastSave="164" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CEAD5A5-683E-40A2-8A9B-9927F8B52FEC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1628,25 +1628,47 @@
       <c r="N19" s="17"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B20" s="14">
+        <v>300</v>
+      </c>
+      <c r="C20" s="14">
+        <v>0</v>
+      </c>
+      <c r="D20" s="14">
+        <v>300</v>
+      </c>
+      <c r="E20" s="14">
+        <v>100</v>
+      </c>
+      <c r="F20" s="14">
+        <v>250</v>
+      </c>
+      <c r="G20" s="14">
+        <v>5</v>
+      </c>
+      <c r="H20" s="14">
+        <v>0</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
+        <v>490</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="N20" s="17"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">

--- a/12603564.xlsx
+++ b/12603564.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c6fb59ddac9459a3/Desktop/excel776/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="164" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CEAD5A5-683E-40A2-8A9B-9927F8B52FEC}"/>
+  <xr:revisionPtr revIDLastSave="169" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22FE949F-8874-4427-BB4D-48B6FEEB582E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -236,6 +236,12 @@
   </si>
   <si>
     <t>avarage</t>
+  </si>
+  <si>
+    <t>Saurabh kumar</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -926,20 +932,26 @@
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20"/>
+      <c r="B2" s="20" t="s">
+        <v>67</v>
+      </c>
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20"/>
+      <c r="F2" s="20">
+        <v>12603664</v>
+      </c>
       <c r="G2" s="20"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20"/>
+      <c r="B3" s="20" t="s">
+        <v>68</v>
+      </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
       <c r="E3" s="6" t="s">

--- a/12603564.xlsx
+++ b/12603564.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c6fb59ddac9459a3/Desktop/excel776/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="169" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22FE949F-8874-4427-BB4D-48B6FEEB582E}"/>
+  <xr:revisionPtr revIDLastSave="219" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7B3D9D6-1D63-4325-B452-52AD339C8431}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -242,6 +242,12 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">very good </t>
+  </si>
+  <si>
+    <t>satisfies</t>
   </si>
 </sst>
 </file>
@@ -522,10 +528,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1684,91 +1686,179 @@
       <c r="N20" s="17"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B21" s="14">
+        <v>300</v>
+      </c>
+      <c r="C21" s="14">
+        <v>0</v>
+      </c>
+      <c r="D21" s="14">
+        <v>200</v>
+      </c>
+      <c r="E21" s="14">
+        <v>100</v>
+      </c>
+      <c r="F21" s="14">
+        <v>250</v>
+      </c>
+      <c r="G21" s="14">
+        <v>5</v>
+      </c>
+      <c r="H21" s="14">
+        <v>0</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
+        <v>590</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="N21" s="17"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B22" s="14">
+        <v>420</v>
+      </c>
+      <c r="C22" s="14">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
+        <v>350</v>
+      </c>
+      <c r="E22" s="14">
+        <v>200</v>
+      </c>
+      <c r="F22" s="14">
+        <v>0</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="H22" s="14">
+        <v>0</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
+        <v>450</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="N22" s="17"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B23" s="14">
+        <v>420</v>
+      </c>
+      <c r="C23" s="14">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
+        <v>350</v>
+      </c>
+      <c r="E23" s="14">
+        <v>200</v>
+      </c>
+      <c r="F23" s="14">
+        <v>0</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="H23" s="14">
+        <v>0</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
+        <v>450</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B24" s="14">
+        <v>300</v>
+      </c>
+      <c r="C24" s="14">
+        <v>20</v>
+      </c>
+      <c r="D24" s="14">
+        <v>200</v>
+      </c>
+      <c r="E24" s="14">
+        <v>100</v>
+      </c>
+      <c r="F24" s="14">
+        <v>300</v>
+      </c>
+      <c r="G24" s="14">
+        <v>6</v>
+      </c>
+      <c r="H24" s="14">
+        <v>20</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
+        <v>500</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="N24" s="17"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">

--- a/12603564.xlsx
+++ b/12603564.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c6fb59ddac9459a3/Desktop/excel776/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="219" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7B3D9D6-1D63-4325-B452-52AD339C8431}"/>
+  <xr:revisionPtr revIDLastSave="231" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B617F8AA-0EB3-43A7-BD19-04A64CEE23C4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t>satisfies</t>
+  </si>
+  <si>
+    <t>bit hard to manage everything sub</t>
   </si>
 </sst>
 </file>
@@ -528,6 +531,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1861,27 +1868,51 @@
       </c>
       <c r="N24" s="17"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+    <row r="25" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B25" s="14">
+        <v>360</v>
+      </c>
+      <c r="C25" s="14">
+        <v>20</v>
+      </c>
+      <c r="D25" s="14">
+        <v>230</v>
+      </c>
+      <c r="E25" s="14">
+        <v>150</v>
+      </c>
+      <c r="F25" s="14">
+        <v>150</v>
+      </c>
+      <c r="G25" s="14">
+        <v>3</v>
+      </c>
+      <c r="H25" s="14">
+        <v>50</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>

--- a/12603564.xlsx
+++ b/12603564.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c6fb59ddac9459a3/Desktop/excel776/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="231" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B617F8AA-0EB3-43A7-BD19-04A64CEE23C4}"/>
+  <xr:revisionPtr revIDLastSave="256" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1338B958-6E1E-459A-918D-EA1EAFB908C7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -251,6 +251,15 @@
   </si>
   <si>
     <t>bit hard to manage everything sub</t>
+  </si>
+  <si>
+    <t>just rest at pg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">low energy because of fresher's party </t>
+  </si>
+  <si>
+    <t>2026-09-</t>
   </si>
 </sst>
 </file>
@@ -1915,51 +1924,101 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B26" s="14">
+        <v>320</v>
+      </c>
+      <c r="C26" s="14">
+        <v>10</v>
+      </c>
+      <c r="D26" s="14">
+        <v>220</v>
+      </c>
+      <c r="E26" s="14">
+        <v>120</v>
+      </c>
+      <c r="F26" s="14">
+        <v>400</v>
+      </c>
+      <c r="G26" s="14">
+        <v>8</v>
+      </c>
+      <c r="H26" s="14">
+        <v>20</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+        <v>350</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B27" s="14">
+        <v>360</v>
+      </c>
+      <c r="C27" s="14">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
+        <v>240</v>
+      </c>
+      <c r="E27" s="14">
+        <v>180</v>
+      </c>
+      <c r="F27" s="14">
+        <v>150</v>
+      </c>
+      <c r="G27" s="14">
+        <v>3</v>
+      </c>
+      <c r="H27" s="14">
+        <v>240</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>250</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
+      <c r="A28" s="13" t="s">
+        <v>74</v>
+      </c>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
       <c r="D28" s="14"/>
